--- a/output/yearly_benthic_cover_iteration_86_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_86_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.72288938708067</v>
+        <v>45.54751180740406</v>
       </c>
       <c r="M2" t="n">
-        <v>99.20983017519202</v>
+        <v>99.19451166814989</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01267555031134</v>
+        <v>87.95201335966594</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94469783282118</v>
+        <v>45.94845254055146</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228680924199313</v>
+        <v>2.22852231179189</v>
       </c>
       <c r="E3" t="n">
-        <v>5.714601039972552</v>
+        <v>5.71330280417763</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428936413997711</v>
+        <v>0.7428407705972968</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97885423947424</v>
+        <v>33.98081397965389</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17310750438947</v>
+        <v>34.17067544747565</v>
       </c>
       <c r="I3" t="n">
-        <v>6.531452942127422</v>
+        <v>6.473103229736488</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643085258748569</v>
+        <v>4.642754816233104</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98732444968865</v>
+        <v>12.04798664033406</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83352682337758</v>
+        <v>48.77118788946562</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7655491058874</v>
+        <v>106.7676270703511</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.07343112397326</v>
+        <v>86.7576689385393</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63293166066991</v>
+        <v>42.37017756033526</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183297641754748</v>
+        <v>2.169529818575686</v>
       </c>
       <c r="E4" t="n">
-        <v>6.507273295427072</v>
+        <v>6.462971968877276</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444447926229606</v>
+        <v>0.7443835325313727</v>
       </c>
       <c r="G4" t="n">
-        <v>33.28693287812154</v>
+        <v>33.08128834889457</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24446046065619</v>
+        <v>34.24164249644313</v>
       </c>
       <c r="I4" t="n">
-        <v>5.454242101497246</v>
+        <v>5.405455694896196</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652779953893504</v>
+        <v>4.652397078321078</v>
       </c>
       <c r="K4" t="n">
-        <v>12.92656887602675</v>
+        <v>13.24233106146069</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25907021491089</v>
+        <v>44.20768295515582</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81857075160755</v>
+        <v>99.82019157695177</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.85133664355615</v>
+        <v>85.32689131021851</v>
       </c>
       <c r="C5" t="n">
-        <v>42.25738775271719</v>
+        <v>41.77815377596035</v>
       </c>
       <c r="D5" t="n">
-        <v>2.123482550200827</v>
+        <v>2.098808543339438</v>
       </c>
       <c r="E5" t="n">
-        <v>7.087868508014792</v>
+        <v>7.004376348443612</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457608791614262</v>
+        <v>0.7456957492156648</v>
       </c>
       <c r="G5" t="n">
-        <v>32.37498166286998</v>
+        <v>32.00292064061951</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30500044142561</v>
+        <v>34.30200446392058</v>
       </c>
       <c r="I5" t="n">
-        <v>4.553237107124601</v>
+        <v>4.512487132081806</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661005494758914</v>
+        <v>4.660598432597904</v>
       </c>
       <c r="K5" t="n">
-        <v>14.14866335644383</v>
+        <v>14.67310868978149</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4424421657974</v>
+        <v>43.39858598717771</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84849327495843</v>
+        <v>99.84984845291955</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.47049348495526</v>
+        <v>83.65944186720446</v>
       </c>
       <c r="C6" t="n">
-        <v>41.58364448430232</v>
+        <v>40.81108616250443</v>
       </c>
       <c r="D6" t="n">
-        <v>2.05605245108503</v>
+        <v>2.016692991306082</v>
       </c>
       <c r="E6" t="n">
-        <v>7.496139234051054</v>
+        <v>7.358006000976462</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468791914424743</v>
+        <v>0.7468147009950704</v>
       </c>
       <c r="G6" t="n">
-        <v>31.34693072730051</v>
+        <v>30.75081143636461</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35644280635383</v>
+        <v>34.35347624577323</v>
       </c>
       <c r="I6" t="n">
-        <v>3.80005412820689</v>
+        <v>3.766048610569826</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667994946515464</v>
+        <v>4.667591881219189</v>
       </c>
       <c r="K6" t="n">
-        <v>15.52950651504474</v>
+        <v>16.34055813279553</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7603701921217</v>
+        <v>42.72300883991998</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87352119146877</v>
+        <v>99.87465313521994</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.78959860390904</v>
+        <v>81.72691294006188</v>
       </c>
       <c r="C7" t="n">
-        <v>40.49289201841715</v>
+        <v>39.46285850952323</v>
       </c>
       <c r="D7" t="n">
-        <v>1.97406860899962</v>
+        <v>1.92202505711244</v>
       </c>
       <c r="E7" t="n">
-        <v>7.725694320236374</v>
+        <v>7.536337970480791</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478326810094004</v>
+        <v>0.7477718674021204</v>
       </c>
       <c r="G7" t="n">
-        <v>30.09699091314204</v>
+        <v>29.30730178665164</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40030332643243</v>
+        <v>34.39750590049753</v>
       </c>
       <c r="I7" t="n">
-        <v>3.170754497780424</v>
+        <v>3.142396186654103</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673954256308752</v>
+        <v>4.673574171263252</v>
       </c>
       <c r="K7" t="n">
-        <v>17.21040139609095</v>
+        <v>18.27308705993811</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19114952637503</v>
+        <v>42.15944196913394</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89444294088314</v>
+        <v>99.89538753859529</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.80131270589364</v>
+        <v>86.78842816175073</v>
       </c>
       <c r="C8" t="n">
-        <v>42.86336586098851</v>
+        <v>41.77822955113481</v>
       </c>
       <c r="D8" t="n">
-        <v>1.978330546742714</v>
+        <v>1.926277292347123</v>
       </c>
       <c r="E8" t="n">
-        <v>9.607496851630092</v>
+        <v>9.386227321956293</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749447222831393</v>
+        <v>0.7494262172610388</v>
       </c>
       <c r="G8" t="n">
-        <v>30.62063158814208</v>
+        <v>29.80872772255477</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47457225024409</v>
+        <v>34.47360599400778</v>
       </c>
       <c r="I8" t="n">
-        <v>5.686789103607051</v>
+        <v>5.760249755742239</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684045142696206</v>
+        <v>4.683913857881491</v>
       </c>
       <c r="K8" t="n">
-        <v>12.19868729410637</v>
+        <v>13.21157183824926</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7487955783837</v>
+        <v>44.8186141416206</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81084873347858</v>
+        <v>99.80841553100467</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.77206800192482</v>
+        <v>84.44825651377472</v>
       </c>
       <c r="C9" t="n">
-        <v>41.71649332532289</v>
+        <v>40.33052159444074</v>
       </c>
       <c r="D9" t="n">
-        <v>1.886689089517308</v>
+        <v>1.820103227412787</v>
       </c>
       <c r="E9" t="n">
-        <v>9.953741547544599</v>
+        <v>9.670423289712225</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508300260206743</v>
+        <v>0.7508488757529251</v>
       </c>
       <c r="G9" t="n">
-        <v>29.20220365934128</v>
+        <v>28.16570685250752</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53818119695104</v>
+        <v>34.53904828463455</v>
       </c>
       <c r="I9" t="n">
-        <v>4.747734819920703</v>
+        <v>4.809320510298947</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692687662629215</v>
+        <v>4.69280547345578</v>
       </c>
       <c r="K9" t="n">
-        <v>14.22793199807519</v>
+        <v>15.55174348622528</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89760831261285</v>
+        <v>43.95772798167447</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84203363601091</v>
+        <v>99.83999306234048</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.50996860663325</v>
+        <v>81.82349651932213</v>
       </c>
       <c r="C10" t="n">
-        <v>40.19077254101015</v>
+        <v>38.45028343291882</v>
       </c>
       <c r="D10" t="n">
-        <v>1.785522381658557</v>
+        <v>1.702414057078867</v>
       </c>
       <c r="E10" t="n">
-        <v>10.08045967669725</v>
+        <v>9.714180373492702</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752017635507057</v>
+        <v>0.7520767824494583</v>
       </c>
       <c r="G10" t="n">
-        <v>27.63634375012213</v>
+        <v>26.34449219752782</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59281123332465</v>
+        <v>34.59553199267507</v>
       </c>
       <c r="I10" t="n">
-        <v>3.962703707404498</v>
+        <v>4.014321225789098</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700110221919108</v>
+        <v>4.700479890309112</v>
       </c>
       <c r="K10" t="n">
-        <v>16.49003139336677</v>
+        <v>18.17650348067787</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1873145428475</v>
+        <v>43.23962085000611</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86811847722441</v>
+        <v>99.86640776360281</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.08450687993057</v>
+        <v>79.22330908331342</v>
       </c>
       <c r="C11" t="n">
-        <v>38.37925723219965</v>
+        <v>36.47052058923308</v>
       </c>
       <c r="D11" t="n">
-        <v>1.678168625756032</v>
+        <v>1.587422011927048</v>
       </c>
       <c r="E11" t="n">
-        <v>10.02550011190854</v>
+        <v>9.616352344991432</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530399139825864</v>
+        <v>0.7531368426656088</v>
       </c>
       <c r="G11" t="n">
-        <v>25.97472061312567</v>
+        <v>24.5650149759417</v>
       </c>
       <c r="H11" t="n">
-        <v>34.639836043199</v>
+        <v>34.64429476261799</v>
       </c>
       <c r="I11" t="n">
-        <v>3.306742109567586</v>
+        <v>3.349982878509609</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706499462391166</v>
+        <v>4.707105266660053</v>
       </c>
       <c r="K11" t="n">
-        <v>18.91549312006941</v>
+        <v>20.77669091668657</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59517454474751</v>
+        <v>42.64127957114177</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88992489701656</v>
+        <v>99.88849107706142</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.42949177883155</v>
+        <v>76.5145804685459</v>
       </c>
       <c r="C12" t="n">
-        <v>36.23568390111371</v>
+        <v>34.27847296055126</v>
       </c>
       <c r="D12" t="n">
-        <v>1.561745206905987</v>
+        <v>1.468994952283295</v>
       </c>
       <c r="E12" t="n">
-        <v>9.789786480401858</v>
+        <v>9.364781828557685</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539228827652839</v>
+        <v>0.7540539037783994</v>
       </c>
       <c r="G12" t="n">
-        <v>24.17271708913984</v>
+        <v>22.73238164224239</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68045260720308</v>
+        <v>34.68647957380636</v>
       </c>
       <c r="I12" t="n">
-        <v>2.758849495132472</v>
+        <v>2.795051669262779</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712018017283025</v>
+        <v>4.712836898614994</v>
       </c>
       <c r="K12" t="n">
-        <v>21.57050822116847</v>
+        <v>23.4854195314541</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10195393022982</v>
+        <v>42.14305242803605</v>
       </c>
       <c r="M12" t="n">
-        <v>99.908146052512</v>
+        <v>99.9069449200414</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.90584095257843</v>
+        <v>73.95899421822283</v>
       </c>
       <c r="C13" t="n">
-        <v>34.13769437395049</v>
+        <v>32.15282769726964</v>
       </c>
       <c r="D13" t="n">
-        <v>1.452264676905309</v>
+        <v>1.358578051299533</v>
       </c>
       <c r="E13" t="n">
-        <v>9.487069498706363</v>
+        <v>9.049488242720415</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546848142556174</v>
+        <v>0.7548463227911451</v>
       </c>
       <c r="G13" t="n">
-        <v>22.4781757089115</v>
+        <v>21.02370379483716</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71550145575842</v>
+        <v>34.72293084839266</v>
       </c>
       <c r="I13" t="n">
-        <v>2.301364708943596</v>
+        <v>2.331657440737261</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71678008909761</v>
+        <v>4.717789517444654</v>
       </c>
       <c r="K13" t="n">
-        <v>24.09415904742158</v>
+        <v>26.04100578177718</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69151187042984</v>
+        <v>41.728526196807</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9233652918019</v>
+        <v>99.92235967585381</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.03162975943081</v>
+        <v>81.6870575561255</v>
       </c>
       <c r="C14" t="n">
-        <v>38.51899196885554</v>
+        <v>36.99866039051162</v>
       </c>
       <c r="D14" t="n">
-        <v>1.454050876057524</v>
+        <v>1.360238357637316</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93011972772107</v>
+        <v>11.71908250489468</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556130316782741</v>
+        <v>0.7557688138711263</v>
       </c>
       <c r="G14" t="n">
-        <v>24.42658440188885</v>
+        <v>23.20878645292975</v>
       </c>
       <c r="H14" t="n">
-        <v>36.67896133136244</v>
+        <v>36.9247552118867</v>
       </c>
       <c r="I14" t="n">
-        <v>3.06371894273345</v>
+        <v>2.99487112821138</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722581447989215</v>
+        <v>4.723555086694537</v>
       </c>
       <c r="K14" t="n">
-        <v>16.96837024056919</v>
+        <v>18.31294244387449</v>
       </c>
       <c r="L14" t="n">
-        <v>44.4106392779198</v>
+        <v>44.588689979286</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89800148734453</v>
+        <v>99.90029281367212</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.2100149232237</v>
+        <v>80.8517866093523</v>
       </c>
       <c r="C15" t="n">
-        <v>38.15294514647508</v>
+        <v>36.61413334530327</v>
       </c>
       <c r="D15" t="n">
-        <v>1.421928114556581</v>
+        <v>1.329123837999867</v>
       </c>
       <c r="E15" t="n">
-        <v>12.10986058878184</v>
+        <v>11.87783618075806</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563960482349654</v>
+        <v>0.7565472483670934</v>
       </c>
       <c r="G15" t="n">
-        <v>23.90429701812518</v>
+        <v>22.68833827787849</v>
       </c>
       <c r="H15" t="n">
-        <v>36.73431304173671</v>
+        <v>36.97322424853808</v>
       </c>
       <c r="I15" t="n">
-        <v>2.555744810319884</v>
+        <v>2.498296513516378</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727475301468536</v>
+        <v>4.728420302294332</v>
       </c>
       <c r="K15" t="n">
-        <v>17.78998507677631</v>
+        <v>19.14821339064768</v>
       </c>
       <c r="L15" t="n">
-        <v>43.97196647278381</v>
+        <v>44.15446239937649</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91489669603519</v>
+        <v>99.91680913532745</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.56212355514556</v>
+        <v>78.1596086023356</v>
       </c>
       <c r="C16" t="n">
-        <v>35.89955495860929</v>
+        <v>34.30665316486406</v>
       </c>
       <c r="D16" t="n">
-        <v>1.322533823456287</v>
+        <v>1.230530991824516</v>
       </c>
       <c r="E16" t="n">
-        <v>11.61864999659244</v>
+        <v>11.34404622078267</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570715796709773</v>
+        <v>0.7572195759642968</v>
       </c>
       <c r="G16" t="n">
-        <v>22.23336117260368</v>
+        <v>21.00534397602967</v>
       </c>
       <c r="H16" t="n">
-        <v>36.76712017141157</v>
+        <v>37.00608157380564</v>
       </c>
       <c r="I16" t="n">
-        <v>2.131689438466995</v>
+        <v>2.08376391415194</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73169737294361</v>
+        <v>4.732622349776852</v>
       </c>
       <c r="K16" t="n">
-        <v>20.43787644485446</v>
+        <v>21.84039139766441</v>
       </c>
       <c r="L16" t="n">
-        <v>43.59157568513849</v>
+        <v>43.78355831209606</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92900708860222</v>
+        <v>99.93060287462453</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.42124936520071</v>
+        <v>80.31055891747809</v>
       </c>
       <c r="C17" t="n">
-        <v>37.23841862781063</v>
+        <v>35.84680018399941</v>
       </c>
       <c r="D17" t="n">
-        <v>1.323692150924562</v>
+        <v>1.231591135907402</v>
       </c>
       <c r="E17" t="n">
-        <v>12.46107925443659</v>
+        <v>12.2822751807248</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577346529252336</v>
+        <v>0.7578719462485378</v>
       </c>
       <c r="G17" t="n">
-        <v>22.72852745044955</v>
+        <v>21.60594515230744</v>
       </c>
       <c r="H17" t="n">
-        <v>37.27501569063263</v>
+        <v>37.62046792688822</v>
       </c>
       <c r="I17" t="n">
-        <v>2.139358585049417</v>
+        <v>2.075707911348337</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735841580782711</v>
+        <v>4.736699664053359</v>
       </c>
       <c r="K17" t="n">
-        <v>18.57875063479932</v>
+        <v>19.68944108252191</v>
       </c>
       <c r="L17" t="n">
-        <v>44.11158118773072</v>
+        <v>44.39462802820863</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92875045034067</v>
+        <v>99.93086929472994</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.77724571803135</v>
+        <v>77.82518606436096</v>
       </c>
       <c r="C18" t="n">
-        <v>34.92416299837902</v>
+        <v>33.68060332753608</v>
       </c>
       <c r="D18" t="n">
-        <v>1.228767795580462</v>
+        <v>1.145281910277736</v>
       </c>
       <c r="E18" t="n">
-        <v>11.86483020284518</v>
+        <v>11.71004664125702</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583066913198334</v>
+        <v>0.7584338491564597</v>
       </c>
       <c r="G18" t="n">
-        <v>21.09862368872697</v>
+        <v>20.0918124659604</v>
       </c>
       <c r="H18" t="n">
-        <v>37.30315580544991</v>
+        <v>37.64836056815847</v>
       </c>
       <c r="I18" t="n">
-        <v>1.784144713360031</v>
+        <v>1.731039072323</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739416820748961</v>
+        <v>4.74021155722787</v>
       </c>
       <c r="K18" t="n">
-        <v>21.22275428196866</v>
+        <v>22.17481393563904</v>
       </c>
       <c r="L18" t="n">
-        <v>43.79365609228985</v>
+        <v>44.08692418373186</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94057337263753</v>
+        <v>99.94234144690699</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.72712910366077</v>
+        <v>76.93243378950412</v>
       </c>
       <c r="C19" t="n">
-        <v>34.14656957687596</v>
+        <v>33.04015798827537</v>
       </c>
       <c r="D19" t="n">
-        <v>1.191721914980099</v>
+        <v>1.114423148493398</v>
       </c>
       <c r="E19" t="n">
-        <v>11.75534059157079</v>
+        <v>11.63721408688017</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587910203470232</v>
+        <v>0.7589123500092122</v>
       </c>
       <c r="G19" t="n">
-        <v>20.46252539837803</v>
+        <v>19.55045365365513</v>
       </c>
       <c r="H19" t="n">
-        <v>37.32698125941091</v>
+        <v>37.67211316392755</v>
       </c>
       <c r="I19" t="n">
-        <v>1.489325041805024</v>
+        <v>1.456115198981079</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742443877168896</v>
+        <v>4.743202187557574</v>
       </c>
       <c r="K19" t="n">
-        <v>22.27287089633922</v>
+        <v>23.06756621049588</v>
       </c>
       <c r="L19" t="n">
-        <v>43.53094704612076</v>
+        <v>43.8437692310403</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95038751933595</v>
+        <v>99.95149342981155</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.94733993151705</v>
+        <v>74.3048744163809</v>
       </c>
       <c r="C20" t="n">
-        <v>31.59544045338293</v>
+        <v>30.63568208799541</v>
       </c>
       <c r="D20" t="n">
-        <v>1.093170094270328</v>
+        <v>1.024329858743239</v>
       </c>
       <c r="E20" t="n">
-        <v>10.99017419743412</v>
+        <v>10.89877537594302</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592100963014221</v>
+        <v>0.759325686760204</v>
       </c>
       <c r="G20" t="n">
-        <v>18.77033604700257</v>
+        <v>17.96993669459248</v>
       </c>
       <c r="H20" t="n">
-        <v>37.34759673834603</v>
+        <v>37.6926310390919</v>
       </c>
       <c r="I20" t="n">
-        <v>1.241789656278699</v>
+        <v>1.214090218998783</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74506310188389</v>
+        <v>4.745785542251273</v>
       </c>
       <c r="K20" t="n">
-        <v>25.05266006848293</v>
+        <v>25.69512558361909</v>
       </c>
       <c r="L20" t="n">
-        <v>43.310529338084</v>
+        <v>43.62874468396935</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95862985994987</v>
+        <v>99.95955235558385</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.31326693521059</v>
+        <v>80.90542930391237</v>
       </c>
       <c r="C21" t="n">
-        <v>35.54862979086044</v>
+        <v>34.81979910078102</v>
       </c>
       <c r="D21" t="n">
-        <v>1.093974542250463</v>
+        <v>1.025024897759145</v>
       </c>
       <c r="E21" t="n">
-        <v>13.11717263903052</v>
+        <v>13.12854213057916</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759768787974081</v>
+        <v>0.7598409123719273</v>
       </c>
       <c r="G21" t="n">
-        <v>20.60387354147124</v>
+        <v>19.93001745456416</v>
       </c>
       <c r="H21" t="n">
-        <v>39.19480496888583</v>
+        <v>39.66609424803858</v>
       </c>
       <c r="I21" t="n">
-        <v>1.795117530760443</v>
+        <v>1.646903958274844</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748554924838007</v>
+        <v>4.749005702324544</v>
       </c>
       <c r="K21" t="n">
-        <v>18.68673306478943</v>
+        <v>19.09457069608763</v>
       </c>
       <c r="L21" t="n">
-        <v>45.70484389430821</v>
+        <v>46.03077062841494</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94020674995807</v>
+        <v>99.9451404252836</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_86_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_86_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.54751180740406</v>
+        <v>45.38636852278296</v>
       </c>
       <c r="M2" t="n">
-        <v>99.19451166814989</v>
+        <v>99.40588532533835</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.95201335966594</v>
+        <v>88.09767526654502</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94845254055146</v>
+        <v>45.94557874685496</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22852231179189</v>
+        <v>2.228898186578094</v>
       </c>
       <c r="E3" t="n">
-        <v>5.71330280417763</v>
+        <v>5.719903629166562</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428407705972968</v>
+        <v>0.742966062192698</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98081397965389</v>
+        <v>33.97823926795683</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17067544747565</v>
+        <v>34.1764388608641</v>
       </c>
       <c r="I3" t="n">
-        <v>6.473103229736488</v>
+        <v>6.607691371082383</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642754816233104</v>
+        <v>4.643537888704362</v>
       </c>
       <c r="K3" t="n">
-        <v>12.04798664033406</v>
+        <v>11.90232473345496</v>
       </c>
       <c r="L3" t="n">
-        <v>48.77118788946562</v>
+        <v>48.9149321158291</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7676270703511</v>
+        <v>106.762835596139</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.7576689385393</v>
+        <v>87.34005950005842</v>
       </c>
       <c r="C4" t="n">
-        <v>42.37017756033526</v>
+        <v>42.8301262920579</v>
       </c>
       <c r="D4" t="n">
-        <v>2.169529818575686</v>
+        <v>2.193231430429714</v>
       </c>
       <c r="E4" t="n">
-        <v>6.462971968877276</v>
+        <v>6.548041531281375</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443835325313727</v>
+        <v>0.744530709227081</v>
       </c>
       <c r="G4" t="n">
-        <v>33.08128834889457</v>
+        <v>33.43452059044196</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24164249644313</v>
+        <v>34.24841262444572</v>
       </c>
       <c r="I4" t="n">
-        <v>5.405455694896196</v>
+        <v>5.518005681563308</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652397078321078</v>
+        <v>4.653316932669256</v>
       </c>
       <c r="K4" t="n">
-        <v>13.24233106146069</v>
+        <v>12.65994049994158</v>
       </c>
       <c r="L4" t="n">
-        <v>44.20768295515582</v>
+        <v>44.32638622547044</v>
       </c>
       <c r="M4" t="n">
-        <v>99.82019157695177</v>
+        <v>99.81645301746993</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.32689131021851</v>
+        <v>86.27407937773955</v>
       </c>
       <c r="C5" t="n">
-        <v>41.77815377596035</v>
+        <v>42.62073381705617</v>
       </c>
       <c r="D5" t="n">
-        <v>2.098808543339438</v>
+        <v>2.141603041674747</v>
       </c>
       <c r="E5" t="n">
-        <v>7.004376348443612</v>
+        <v>7.161655166487907</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7456957492156648</v>
+        <v>0.7458558261348358</v>
       </c>
       <c r="G5" t="n">
-        <v>32.00292064061951</v>
+        <v>32.64747623072243</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30200446392058</v>
+        <v>34.30936800220244</v>
       </c>
       <c r="I5" t="n">
-        <v>4.512487132081806</v>
+        <v>4.606522197174469</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660598432597904</v>
+        <v>4.661598913342724</v>
       </c>
       <c r="K5" t="n">
-        <v>14.67310868978149</v>
+        <v>13.72592062226044</v>
       </c>
       <c r="L5" t="n">
-        <v>43.39858598717771</v>
+        <v>43.5000676250844</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84984845291955</v>
+        <v>99.84672206440101</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.65944186720446</v>
+        <v>84.99824269699839</v>
       </c>
       <c r="C6" t="n">
-        <v>40.81108616250443</v>
+        <v>42.06054833388632</v>
       </c>
       <c r="D6" t="n">
-        <v>2.016692991306082</v>
+        <v>2.07960172615432</v>
       </c>
       <c r="E6" t="n">
-        <v>7.358006000976462</v>
+        <v>7.595078239064588</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468147009950704</v>
+        <v>0.7469803531670474</v>
       </c>
       <c r="G6" t="n">
-        <v>30.75081143636461</v>
+        <v>31.70230271567936</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35347624577323</v>
+        <v>34.36109624568417</v>
       </c>
       <c r="I6" t="n">
-        <v>3.766048610569826</v>
+        <v>3.844556209954852</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667591881219189</v>
+        <v>4.668627207294047</v>
       </c>
       <c r="K6" t="n">
-        <v>16.34055813279553</v>
+        <v>15.00175730300161</v>
       </c>
       <c r="L6" t="n">
-        <v>42.72300883991998</v>
+        <v>42.80973541319055</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87465313521994</v>
+        <v>99.87204105007849</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81.72691294006188</v>
+        <v>83.60127049963367</v>
       </c>
       <c r="C7" t="n">
-        <v>39.46285850952323</v>
+        <v>41.2609569769721</v>
       </c>
       <c r="D7" t="n">
-        <v>1.92202505711244</v>
+        <v>2.011960187790065</v>
       </c>
       <c r="E7" t="n">
-        <v>7.536337970480791</v>
+        <v>7.882688324514123</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477718674021204</v>
+        <v>0.7479357749603761</v>
       </c>
       <c r="G7" t="n">
-        <v>29.30730178665164</v>
+        <v>30.6711473274102</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39750590049753</v>
+        <v>34.4050456481773</v>
       </c>
       <c r="I7" t="n">
-        <v>3.142396186654103</v>
+        <v>3.207894643279265</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673574171263252</v>
+        <v>4.674598593502352</v>
       </c>
       <c r="K7" t="n">
-        <v>18.27308705993811</v>
+        <v>16.39872950036634</v>
       </c>
       <c r="L7" t="n">
-        <v>42.15944196913394</v>
+        <v>42.23352029460726</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89538753859529</v>
+        <v>99.8932067719457</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86.78842816175073</v>
+        <v>88.40821820965792</v>
       </c>
       <c r="C8" t="n">
-        <v>41.77822955113481</v>
+        <v>43.46263493726191</v>
       </c>
       <c r="D8" t="n">
-        <v>1.926277292347123</v>
+        <v>2.01627570776144</v>
       </c>
       <c r="E8" t="n">
-        <v>9.386227321956293</v>
+        <v>9.651320734732876</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494262172610388</v>
+        <v>0.7495400471491279</v>
       </c>
       <c r="G8" t="n">
-        <v>29.80872772255477</v>
+        <v>31.13872289123252</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47360599400778</v>
+        <v>34.47884216885988</v>
       </c>
       <c r="I8" t="n">
-        <v>5.760249755742239</v>
+        <v>5.68889136524003</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683913857881491</v>
+        <v>4.684625294682051</v>
       </c>
       <c r="K8" t="n">
-        <v>13.21157183824926</v>
+        <v>11.59178179034206</v>
       </c>
       <c r="L8" t="n">
-        <v>44.8186141416206</v>
+        <v>44.7563594326955</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80841553100467</v>
+        <v>99.81077616029948</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.44825651377472</v>
+        <v>86.51891768587018</v>
       </c>
       <c r="C9" t="n">
-        <v>40.33052159444074</v>
+        <v>42.45668265781596</v>
       </c>
       <c r="D9" t="n">
-        <v>1.820103227412787</v>
+        <v>1.930811907153092</v>
       </c>
       <c r="E9" t="n">
-        <v>9.670423289712225</v>
+        <v>10.03380015911577</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508488757529251</v>
+        <v>0.7509115693990439</v>
       </c>
       <c r="G9" t="n">
-        <v>28.16570685250752</v>
+        <v>29.81884704581576</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53904828463455</v>
+        <v>34.54193219235602</v>
       </c>
       <c r="I9" t="n">
-        <v>4.809320510298947</v>
+        <v>4.749417503286447</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69280547345578</v>
+        <v>4.693197308744026</v>
       </c>
       <c r="K9" t="n">
-        <v>15.55174348622528</v>
+        <v>13.48108231412985</v>
       </c>
       <c r="L9" t="n">
-        <v>43.95772798167447</v>
+        <v>43.90421026790862</v>
       </c>
       <c r="M9" t="n">
-        <v>99.83999306234048</v>
+        <v>99.84197523985443</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>81.82349651932213</v>
+        <v>84.5063057975232</v>
       </c>
       <c r="C10" t="n">
-        <v>38.45028343291882</v>
+        <v>41.18140011303759</v>
       </c>
       <c r="D10" t="n">
-        <v>1.702414057078867</v>
+        <v>1.840682804599665</v>
       </c>
       <c r="E10" t="n">
-        <v>9.714180373492702</v>
+        <v>10.22610132840127</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520767824494583</v>
+        <v>0.7520856990655302</v>
       </c>
       <c r="G10" t="n">
-        <v>26.34449219752782</v>
+        <v>28.42692175601373</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59553199267507</v>
+        <v>34.59594215701439</v>
       </c>
       <c r="I10" t="n">
-        <v>4.014321225789098</v>
+        <v>3.96403643326904</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700479890309112</v>
+        <v>4.700535619159565</v>
       </c>
       <c r="K10" t="n">
-        <v>18.17650348067787</v>
+        <v>15.49369420247682</v>
       </c>
       <c r="L10" t="n">
-        <v>43.23962085000611</v>
+        <v>43.19297742050542</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86640776360281</v>
+        <v>99.86807173601983</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.22330908331342</v>
+        <v>82.24000347357696</v>
       </c>
       <c r="C11" t="n">
-        <v>36.47052058923308</v>
+        <v>39.53004987986579</v>
       </c>
       <c r="D11" t="n">
-        <v>1.587422011927048</v>
+        <v>1.739995415898431</v>
       </c>
       <c r="E11" t="n">
-        <v>9.616352344991432</v>
+        <v>10.21802101247858</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7531368426656088</v>
+        <v>0.7530940256534563</v>
       </c>
       <c r="G11" t="n">
-        <v>24.5650149759417</v>
+        <v>26.87193764181713</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64429476261799</v>
+        <v>34.64232518005899</v>
       </c>
       <c r="I11" t="n">
-        <v>3.349982878509609</v>
+        <v>3.307792537336269</v>
       </c>
       <c r="J11" t="n">
-        <v>4.707105266660053</v>
+        <v>4.706837660334103</v>
       </c>
       <c r="K11" t="n">
-        <v>20.77669091668657</v>
+        <v>17.75999652642303</v>
       </c>
       <c r="L11" t="n">
-        <v>42.64127957114177</v>
+        <v>42.59984147056483</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88849107706142</v>
+        <v>99.88988787685365</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>76.5145804685459</v>
+        <v>79.88518883369012</v>
       </c>
       <c r="C12" t="n">
-        <v>34.27847296055126</v>
+        <v>37.68764908614635</v>
       </c>
       <c r="D12" t="n">
-        <v>1.468994952283295</v>
+        <v>1.6363567660184</v>
       </c>
       <c r="E12" t="n">
-        <v>9.364781828557685</v>
+        <v>10.06935377427266</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7540539037783994</v>
+        <v>0.7539612241316149</v>
       </c>
       <c r="G12" t="n">
-        <v>22.73238164224239</v>
+        <v>25.27137518549576</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68647957380636</v>
+        <v>34.68221631005429</v>
       </c>
       <c r="I12" t="n">
-        <v>2.795051669262779</v>
+        <v>2.759667922894806</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712836898614994</v>
+        <v>4.712257650822594</v>
       </c>
       <c r="K12" t="n">
-        <v>23.4854195314541</v>
+        <v>20.11481116630987</v>
       </c>
       <c r="L12" t="n">
-        <v>42.14305242803605</v>
+        <v>42.10565662150665</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9069449200414</v>
+        <v>99.90811687396287</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>73.95899421822283</v>
+        <v>77.53953619896868</v>
       </c>
       <c r="C13" t="n">
-        <v>32.15282769726964</v>
+        <v>35.76868152671011</v>
       </c>
       <c r="D13" t="n">
-        <v>1.358578051299533</v>
+        <v>1.534070597782855</v>
       </c>
       <c r="E13" t="n">
-        <v>9.049488242720415</v>
+        <v>9.823600325265206</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7548463227911451</v>
+        <v>0.7547073458865121</v>
       </c>
       <c r="G13" t="n">
-        <v>21.02370379483716</v>
+        <v>23.69170002696855</v>
       </c>
       <c r="H13" t="n">
-        <v>34.72293084839266</v>
+        <v>34.71653791077956</v>
       </c>
       <c r="I13" t="n">
-        <v>2.331657440737261</v>
+        <v>2.301999080495274</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717789517444654</v>
+        <v>4.716920911790702</v>
       </c>
       <c r="K13" t="n">
-        <v>26.04100578177718</v>
+        <v>22.46046380103137</v>
       </c>
       <c r="L13" t="n">
-        <v>41.728526196807</v>
+        <v>41.69419722995588</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92235967585381</v>
+        <v>99.92334255769735</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>81.6870575561255</v>
+        <v>83.92013106672825</v>
       </c>
       <c r="C14" t="n">
-        <v>36.99866039051162</v>
+        <v>39.68828284680233</v>
       </c>
       <c r="D14" t="n">
-        <v>1.360238357637316</v>
+        <v>1.535904833539928</v>
       </c>
       <c r="E14" t="n">
-        <v>11.71908250489468</v>
+        <v>12.03062152677774</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7557688138711263</v>
+        <v>0.7556097236531878</v>
       </c>
       <c r="G14" t="n">
-        <v>23.20878645292975</v>
+        <v>25.41360068551248</v>
       </c>
       <c r="H14" t="n">
-        <v>36.9247552118867</v>
+        <v>36.45162059099292</v>
       </c>
       <c r="I14" t="n">
-        <v>2.99487112821138</v>
+        <v>3.01021293341957</v>
       </c>
       <c r="J14" t="n">
-        <v>4.723555086694537</v>
+        <v>4.722560772832424</v>
       </c>
       <c r="K14" t="n">
-        <v>18.31294244387449</v>
+        <v>16.07986893327174</v>
       </c>
       <c r="L14" t="n">
-        <v>44.588689979286</v>
+        <v>44.13162761915731</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90029281367212</v>
+        <v>99.89977939923139</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>80.8517866093523</v>
+        <v>83.17789053240949</v>
       </c>
       <c r="C15" t="n">
-        <v>36.61413334530327</v>
+        <v>39.41158136480619</v>
       </c>
       <c r="D15" t="n">
-        <v>1.329123837999867</v>
+        <v>1.508175021501394</v>
       </c>
       <c r="E15" t="n">
-        <v>11.87783618075806</v>
+        <v>12.23192193925683</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7565472483670934</v>
+        <v>0.7563700869753303</v>
       </c>
       <c r="G15" t="n">
-        <v>22.68833827787849</v>
+        <v>24.9547738397063</v>
       </c>
       <c r="H15" t="n">
-        <v>36.97322424853808</v>
+        <v>36.48830153151343</v>
       </c>
       <c r="I15" t="n">
-        <v>2.498296513516378</v>
+        <v>2.511035069860409</v>
       </c>
       <c r="J15" t="n">
-        <v>4.728420302294332</v>
+        <v>4.727313043595815</v>
       </c>
       <c r="K15" t="n">
-        <v>19.14821339064768</v>
+        <v>16.8221094675905</v>
       </c>
       <c r="L15" t="n">
-        <v>44.15446239937649</v>
+        <v>43.68269214167498</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91680913532745</v>
+        <v>99.91638297407167</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.1596086023356</v>
+        <v>80.80084372097895</v>
       </c>
       <c r="C16" t="n">
-        <v>34.30665316486406</v>
+        <v>37.42294894682325</v>
       </c>
       <c r="D16" t="n">
-        <v>1.230530991824516</v>
+        <v>1.416750018645406</v>
       </c>
       <c r="E16" t="n">
-        <v>11.34404622078267</v>
+        <v>11.8394836215184</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7572195759642968</v>
+        <v>0.7570235842661395</v>
       </c>
       <c r="G16" t="n">
-        <v>21.00534397602967</v>
+        <v>23.44202483044711</v>
       </c>
       <c r="H16" t="n">
-        <v>37.00608157380564</v>
+        <v>36.5198271121884</v>
       </c>
       <c r="I16" t="n">
-        <v>2.08376391415194</v>
+        <v>2.094337152250116</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732622349776852</v>
+        <v>4.731397401663372</v>
       </c>
       <c r="K16" t="n">
-        <v>21.84039139766441</v>
+        <v>19.19915627902105</v>
       </c>
       <c r="L16" t="n">
-        <v>43.78355831209606</v>
+        <v>43.30814379999292</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93060287462453</v>
+        <v>99.93024902583721</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.31055891747809</v>
+        <v>82.27170794895855</v>
       </c>
       <c r="C17" t="n">
-        <v>35.84680018399941</v>
+        <v>38.50356311544569</v>
       </c>
       <c r="D17" t="n">
-        <v>1.231591135907402</v>
+        <v>1.4179551279072</v>
       </c>
       <c r="E17" t="n">
-        <v>12.2822751807248</v>
+        <v>12.54909477654149</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578719462485378</v>
+        <v>0.7576675201198815</v>
       </c>
       <c r="G17" t="n">
-        <v>21.60594515230744</v>
+        <v>23.81159741130189</v>
       </c>
       <c r="H17" t="n">
-        <v>37.62046792688822</v>
+        <v>36.90052387193588</v>
       </c>
       <c r="I17" t="n">
-        <v>2.075707911348337</v>
+        <v>2.099447240402955</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736699664053359</v>
+        <v>4.735422000749259</v>
       </c>
       <c r="K17" t="n">
-        <v>19.68944108252191</v>
+        <v>17.72829205104144</v>
       </c>
       <c r="L17" t="n">
-        <v>44.39462802820863</v>
+        <v>43.69822273564</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93086929472994</v>
+        <v>99.93007790212712</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.82518606436096</v>
+        <v>79.97785443798591</v>
       </c>
       <c r="C18" t="n">
-        <v>33.68060332753608</v>
+        <v>36.53405121939821</v>
       </c>
       <c r="D18" t="n">
-        <v>1.145281910277736</v>
+        <v>1.332831237341751</v>
       </c>
       <c r="E18" t="n">
-        <v>11.71004664125702</v>
+        <v>12.08753949523475</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584338491564597</v>
+        <v>0.758220396680599</v>
       </c>
       <c r="G18" t="n">
-        <v>20.0918124659604</v>
+        <v>22.38211930417745</v>
       </c>
       <c r="H18" t="n">
-        <v>37.64836056815847</v>
+        <v>36.92745050424521</v>
       </c>
       <c r="I18" t="n">
-        <v>1.731039072323</v>
+        <v>1.750816021052402</v>
       </c>
       <c r="J18" t="n">
-        <v>4.74021155722787</v>
+        <v>4.738877479253744</v>
       </c>
       <c r="K18" t="n">
-        <v>22.17481393563904</v>
+        <v>20.02214556201411</v>
       </c>
       <c r="L18" t="n">
-        <v>44.08692418373186</v>
+        <v>43.3854852396876</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94234144690699</v>
+        <v>99.94168202109991</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.93243378950412</v>
+        <v>79.0202184573554</v>
       </c>
       <c r="C19" t="n">
-        <v>33.04015798827537</v>
+        <v>35.84624334461687</v>
       </c>
       <c r="D19" t="n">
-        <v>1.114423148493398</v>
+        <v>1.297979857899283</v>
       </c>
       <c r="E19" t="n">
-        <v>11.63721408688017</v>
+        <v>12.01478854786225</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589123500092122</v>
+        <v>0.7586873383390705</v>
       </c>
       <c r="G19" t="n">
-        <v>19.55045365365513</v>
+        <v>21.79686311363961</v>
       </c>
       <c r="H19" t="n">
-        <v>37.67211316392755</v>
+        <v>36.95019186685833</v>
       </c>
       <c r="I19" t="n">
-        <v>1.456115198981079</v>
+        <v>1.459911868137646</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743202187557574</v>
+        <v>4.741795864619191</v>
       </c>
       <c r="K19" t="n">
-        <v>23.06756621049588</v>
+        <v>20.97978154264462</v>
       </c>
       <c r="L19" t="n">
-        <v>43.8437692310403</v>
+        <v>43.12534133437596</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95149342981155</v>
+        <v>99.95136622163744</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.3048744163809</v>
+        <v>76.47680467996321</v>
       </c>
       <c r="C20" t="n">
-        <v>30.63568208799541</v>
+        <v>33.52767061758934</v>
       </c>
       <c r="D20" t="n">
-        <v>1.024329858743239</v>
+        <v>1.204590286796886</v>
       </c>
       <c r="E20" t="n">
-        <v>10.89877537594302</v>
+        <v>11.35319836345353</v>
       </c>
       <c r="F20" t="n">
-        <v>0.759325686760204</v>
+        <v>0.7590898584590183</v>
       </c>
       <c r="G20" t="n">
-        <v>17.96993669459248</v>
+        <v>20.22858015056267</v>
       </c>
       <c r="H20" t="n">
-        <v>37.6926310390919</v>
+        <v>36.96979572066048</v>
       </c>
       <c r="I20" t="n">
-        <v>1.214090218998783</v>
+        <v>1.217238684661748</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745785542251273</v>
+        <v>4.744311615368865</v>
       </c>
       <c r="K20" t="n">
-        <v>25.69512558361909</v>
+        <v>23.52319532003683</v>
       </c>
       <c r="L20" t="n">
-        <v>43.62874468396935</v>
+        <v>42.90858095492556</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95955235558385</v>
+        <v>99.95944689255171</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.90542930391237</v>
+        <v>81.95619387176772</v>
       </c>
       <c r="C21" t="n">
-        <v>34.81979910078102</v>
+        <v>36.86135831922786</v>
       </c>
       <c r="D21" t="n">
-        <v>1.025024897759145</v>
+        <v>1.205479411283216</v>
       </c>
       <c r="E21" t="n">
-        <v>13.12854213057916</v>
+        <v>13.17198435450811</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598409123719273</v>
+        <v>0.7596501530154983</v>
       </c>
       <c r="G21" t="n">
-        <v>19.93001745456416</v>
+        <v>21.7514522707154</v>
       </c>
       <c r="H21" t="n">
-        <v>39.66609424803858</v>
+        <v>38.50502475988973</v>
       </c>
       <c r="I21" t="n">
-        <v>1.646903958274844</v>
+        <v>1.8147894660089</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749005702324544</v>
+        <v>4.747813456346865</v>
       </c>
       <c r="K21" t="n">
-        <v>19.09457069608763</v>
+        <v>18.04380612823228</v>
       </c>
       <c r="L21" t="n">
-        <v>46.03077062841494</v>
+        <v>45.03438718810014</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9451404252836</v>
+        <v>99.93955163556028</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_86_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_86_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.38636852278296</v>
+        <v>43.79226765348322</v>
       </c>
       <c r="M2" t="n">
-        <v>99.40588532533835</v>
+        <v>94.8732114775157</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.09767526654502</v>
+        <v>81.42203044958957</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94557874685496</v>
+        <v>43.17758600514513</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228898186578094</v>
+        <v>2.176210089953774</v>
       </c>
       <c r="E3" t="n">
-        <v>5.719903629166562</v>
+        <v>4.16179167452975</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742966062192698</v>
+        <v>0.7375942278441459</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97823926795683</v>
+        <v>32.73382676972135</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1764388608641</v>
+        <v>33.9293344808307</v>
       </c>
       <c r="I3" t="n">
-        <v>6.607691371082383</v>
+        <v>3.073309282683941</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643537888704362</v>
+        <v>4.609963924025911</v>
       </c>
       <c r="K3" t="n">
-        <v>11.90232473345496</v>
+        <v>18.57796955041042</v>
       </c>
       <c r="L3" t="n">
-        <v>48.9149321158291</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.762835596139</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.34005950005842</v>
+        <v>88.37166405651493</v>
       </c>
       <c r="C4" t="n">
-        <v>42.8301262920579</v>
+        <v>42.73653369154083</v>
       </c>
       <c r="D4" t="n">
-        <v>2.193231430429714</v>
+        <v>2.181861486368405</v>
       </c>
       <c r="E4" t="n">
-        <v>6.548041531281375</v>
+        <v>6.511561366382995</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744530709227081</v>
+        <v>0.7395096850851236</v>
       </c>
       <c r="G4" t="n">
-        <v>33.43452059044196</v>
+        <v>33.41458358797988</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24841262444572</v>
+        <v>34.01744551391567</v>
       </c>
       <c r="I4" t="n">
-        <v>5.518005681563308</v>
+        <v>6.884766885000849</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653316932669256</v>
+        <v>4.621935531782022</v>
       </c>
       <c r="K4" t="n">
-        <v>12.65994049994158</v>
+        <v>11.62833594348504</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32638622547044</v>
+        <v>45.40623255980904</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81645301746993</v>
+        <v>99.77110219483492</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.27407937773955</v>
+        <v>86.95372808911287</v>
       </c>
       <c r="C5" t="n">
-        <v>42.62073381705617</v>
+        <v>42.38579778133109</v>
       </c>
       <c r="D5" t="n">
-        <v>2.141603041674747</v>
+        <v>2.113037304543348</v>
       </c>
       <c r="E5" t="n">
-        <v>7.161655166487907</v>
+        <v>7.264487374273242</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458558261348358</v>
+        <v>0.7411397264486121</v>
       </c>
       <c r="G5" t="n">
-        <v>32.64747623072243</v>
+        <v>32.36056096058777</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30936800220244</v>
+        <v>34.09242741663615</v>
       </c>
       <c r="I5" t="n">
-        <v>4.606522197174469</v>
+        <v>5.749952016319937</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661598913342724</v>
+        <v>4.632123290303825</v>
       </c>
       <c r="K5" t="n">
-        <v>13.72592062226044</v>
+        <v>13.04627191088714</v>
       </c>
       <c r="L5" t="n">
-        <v>43.5000676250844</v>
+        <v>44.3766867831984</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84672206440101</v>
+        <v>99.80875647541663</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.99824269699839</v>
+        <v>85.24997313441354</v>
       </c>
       <c r="C6" t="n">
-        <v>42.06054833388632</v>
+        <v>41.57407485786477</v>
       </c>
       <c r="D6" t="n">
-        <v>2.07960172615432</v>
+        <v>2.030587228692608</v>
       </c>
       <c r="E6" t="n">
-        <v>7.595078239064588</v>
+        <v>7.781132764556276</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469803531670474</v>
+        <v>0.7425309022074319</v>
       </c>
       <c r="G6" t="n">
-        <v>31.70230271567936</v>
+        <v>31.09786166983881</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36109624568417</v>
+        <v>34.15642150154186</v>
       </c>
       <c r="I6" t="n">
-        <v>3.844556209954852</v>
+        <v>4.800620928780106</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668627207294047</v>
+        <v>4.640818138796448</v>
       </c>
       <c r="K6" t="n">
-        <v>15.00175730300161</v>
+        <v>14.75002686558644</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80973541319055</v>
+        <v>43.51617738720658</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87204105007849</v>
+        <v>99.8402791106578</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.60127049963367</v>
+        <v>83.34456411121693</v>
       </c>
       <c r="C7" t="n">
-        <v>41.2609569769721</v>
+        <v>40.4134564488735</v>
       </c>
       <c r="D7" t="n">
-        <v>2.011960187790065</v>
+        <v>1.939112946062385</v>
       </c>
       <c r="E7" t="n">
-        <v>7.882688324514123</v>
+        <v>8.098428219823065</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479357749603761</v>
+        <v>0.7437208491302454</v>
       </c>
       <c r="G7" t="n">
-        <v>30.6711473274102</v>
+        <v>29.69695923758332</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4050456481773</v>
+        <v>34.21115905999127</v>
       </c>
       <c r="I7" t="n">
-        <v>3.207894643279265</v>
+        <v>4.006928491562598</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674598593502352</v>
+        <v>4.648255307064033</v>
       </c>
       <c r="K7" t="n">
-        <v>16.39872950036634</v>
+        <v>16.65543588878308</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23352029460726</v>
+        <v>42.79775708098839</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8932067719457</v>
+        <v>99.86664941864498</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.40821820965792</v>
+        <v>81.22051597638313</v>
       </c>
       <c r="C8" t="n">
-        <v>43.46263493726191</v>
+        <v>38.91069096381558</v>
       </c>
       <c r="D8" t="n">
-        <v>2.01627570776144</v>
+        <v>1.837974428111816</v>
       </c>
       <c r="E8" t="n">
-        <v>9.651320734732876</v>
+        <v>8.23331918472029</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495400471491279</v>
+        <v>0.7447414333838391</v>
       </c>
       <c r="G8" t="n">
-        <v>31.13872289123252</v>
+        <v>28.14805181007806</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47884216885988</v>
+        <v>34.25810593565659</v>
       </c>
       <c r="I8" t="n">
-        <v>5.68889136524003</v>
+        <v>3.34368922578355</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684625294682051</v>
+        <v>4.654633958648994</v>
       </c>
       <c r="K8" t="n">
-        <v>11.59178179034206</v>
+        <v>18.77948402361688</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7563594326955</v>
+        <v>42.19852144335747</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81077616029948</v>
+        <v>99.88869643078993</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.51891768587018</v>
+        <v>79.03550549691494</v>
       </c>
       <c r="C9" t="n">
-        <v>42.45668265781596</v>
+        <v>37.24347765818465</v>
       </c>
       <c r="D9" t="n">
-        <v>1.930811907153092</v>
+        <v>1.734935771725122</v>
       </c>
       <c r="E9" t="n">
-        <v>10.03380015911577</v>
+        <v>8.236698877970683</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7509115693990439</v>
+        <v>0.7456176618469542</v>
       </c>
       <c r="G9" t="n">
-        <v>29.81884704581576</v>
+        <v>26.5700443067892</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54193219235602</v>
+        <v>34.29841244495988</v>
       </c>
       <c r="I9" t="n">
-        <v>4.749417503286447</v>
+        <v>2.789686047079638</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693197308744026</v>
+        <v>4.660110386543463</v>
       </c>
       <c r="K9" t="n">
-        <v>13.48108231412985</v>
+        <v>20.96449450308505</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90421026790862</v>
+        <v>41.69914758245854</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84197523985443</v>
+        <v>99.90711974372824</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.5063057975232</v>
+        <v>84.65054154121086</v>
       </c>
       <c r="C10" t="n">
-        <v>41.18140011303759</v>
+        <v>41.15463243322696</v>
       </c>
       <c r="D10" t="n">
-        <v>1.840682804599665</v>
+        <v>1.736810212704745</v>
       </c>
       <c r="E10" t="n">
-        <v>10.22610132840127</v>
+        <v>10.4099980553972</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520856990655302</v>
+        <v>0.7464232342048903</v>
       </c>
       <c r="G10" t="n">
-        <v>28.42692175601373</v>
+        <v>28.30586478415975</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59594215701439</v>
+        <v>36.04258272419623</v>
       </c>
       <c r="I10" t="n">
-        <v>3.96403643326904</v>
+        <v>2.743717316767473</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700535619159565</v>
+        <v>4.665145213780564</v>
       </c>
       <c r="K10" t="n">
-        <v>15.49369420247682</v>
+        <v>15.34945845878916</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19297742050542</v>
+        <v>43.40455056871955</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86807173601983</v>
+        <v>99.90864146073567</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.24000347357696</v>
+        <v>84.10106716862094</v>
       </c>
       <c r="C11" t="n">
-        <v>39.53004987986579</v>
+        <v>40.90536548774976</v>
       </c>
       <c r="D11" t="n">
-        <v>1.739995415898431</v>
+        <v>1.704600462264852</v>
       </c>
       <c r="E11" t="n">
-        <v>10.21802101247858</v>
+        <v>10.66075082384369</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530940256534563</v>
+        <v>0.7471218211149364</v>
       </c>
       <c r="G11" t="n">
-        <v>26.87193764181713</v>
+        <v>27.83117622750597</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64232518005899</v>
+        <v>36.1265689980788</v>
       </c>
       <c r="I11" t="n">
-        <v>3.307792537336269</v>
+        <v>2.361337453844341</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706837660334103</v>
+        <v>4.669511381968352</v>
       </c>
       <c r="K11" t="n">
-        <v>17.75999652642303</v>
+        <v>15.89893283137906</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59984147056483</v>
+        <v>43.11706403037768</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88988787685365</v>
+        <v>99.9213623495065</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.88518883369012</v>
+        <v>81.94860496201389</v>
       </c>
       <c r="C12" t="n">
-        <v>37.68764908614635</v>
+        <v>39.11915066337856</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6363567660184</v>
+        <v>1.614614087690862</v>
       </c>
       <c r="E12" t="n">
-        <v>10.06935377427266</v>
+        <v>10.42619281139311</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539612241316149</v>
+        <v>0.7477203059702734</v>
       </c>
       <c r="G12" t="n">
-        <v>25.27137518549576</v>
+        <v>26.36196000688174</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68221631005429</v>
+        <v>36.15550832739509</v>
       </c>
       <c r="I12" t="n">
-        <v>2.759667922894806</v>
+        <v>1.969357510368598</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712257650822594</v>
+        <v>4.673251912314208</v>
       </c>
       <c r="K12" t="n">
-        <v>20.11481116630987</v>
+        <v>18.0513950379861</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10565662150665</v>
+        <v>42.7638615915841</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90811687396287</v>
+        <v>99.93440729294878</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.53953619896868</v>
+        <v>83.23976027273113</v>
       </c>
       <c r="C13" t="n">
-        <v>35.76868152671011</v>
+        <v>40.18456494424064</v>
       </c>
       <c r="D13" t="n">
-        <v>1.534070597782855</v>
+        <v>1.615778344649568</v>
       </c>
       <c r="E13" t="n">
-        <v>9.823600325265206</v>
+        <v>11.10117772231362</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547073458865121</v>
+        <v>0.7482594679756274</v>
       </c>
       <c r="G13" t="n">
-        <v>23.69170002696855</v>
+        <v>26.74832547220478</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71653791077956</v>
+        <v>36.54893567014724</v>
       </c>
       <c r="I13" t="n">
-        <v>2.301999080495274</v>
+        <v>1.800661920592629</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716920911790702</v>
+        <v>4.67662167484767</v>
       </c>
       <c r="K13" t="n">
-        <v>22.46046380103137</v>
+        <v>16.76023972726887</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69419722995588</v>
+        <v>42.9952165136614</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92334255769735</v>
+        <v>99.94002118517091</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.92013106672825</v>
+        <v>80.99591698981281</v>
       </c>
       <c r="C14" t="n">
-        <v>39.68828284680233</v>
+        <v>38.2197896576409</v>
       </c>
       <c r="D14" t="n">
-        <v>1.535904833539928</v>
+        <v>1.524853097672979</v>
       </c>
       <c r="E14" t="n">
-        <v>12.03062152677774</v>
+        <v>10.72672382568754</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556097236531878</v>
+        <v>0.7487218352116998</v>
       </c>
       <c r="G14" t="n">
-        <v>25.41360068551248</v>
+        <v>25.24310781173547</v>
       </c>
       <c r="H14" t="n">
-        <v>36.45162059099292</v>
+        <v>36.57152012258713</v>
       </c>
       <c r="I14" t="n">
-        <v>3.01021293341957</v>
+        <v>1.501478826844874</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722560772832424</v>
+        <v>4.679511470073122</v>
       </c>
       <c r="K14" t="n">
-        <v>16.07986893327174</v>
+        <v>19.00408301018721</v>
       </c>
       <c r="L14" t="n">
-        <v>44.13162761915731</v>
+        <v>42.72610894548876</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89977939923139</v>
+        <v>99.94998161331687</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.17789053240949</v>
+        <v>80.01958853289342</v>
       </c>
       <c r="C15" t="n">
-        <v>39.41158136480619</v>
+        <v>37.44153901298611</v>
       </c>
       <c r="D15" t="n">
-        <v>1.508175021501394</v>
+        <v>1.484331898149031</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23192193925683</v>
+        <v>10.65582331255158</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563700869753303</v>
+        <v>0.7491225834962986</v>
       </c>
       <c r="G15" t="n">
-        <v>24.9547738397063</v>
+        <v>24.57230154862404</v>
       </c>
       <c r="H15" t="n">
-        <v>36.48830153151343</v>
+        <v>36.59109478071121</v>
       </c>
       <c r="I15" t="n">
-        <v>2.511035069860409</v>
+        <v>1.284898262509395</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727313043595815</v>
+        <v>4.682016146851865</v>
       </c>
       <c r="K15" t="n">
-        <v>16.8221094675905</v>
+        <v>19.98041146710658</v>
       </c>
       <c r="L15" t="n">
-        <v>43.68269214167498</v>
+        <v>42.53524248999614</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91638297407167</v>
+        <v>99.95719297008883</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.80084372097895</v>
+        <v>77.43818111934688</v>
       </c>
       <c r="C16" t="n">
-        <v>37.42294894682325</v>
+        <v>35.05863002128958</v>
       </c>
       <c r="D16" t="n">
-        <v>1.416750018645406</v>
+        <v>1.380598596894773</v>
       </c>
       <c r="E16" t="n">
-        <v>11.8394836215184</v>
+        <v>10.08967597948619</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570235842661395</v>
+        <v>0.7494680167964373</v>
       </c>
       <c r="G16" t="n">
-        <v>23.44202483044711</v>
+        <v>22.85505356504811</v>
       </c>
       <c r="H16" t="n">
-        <v>36.5198271121884</v>
+        <v>36.60796756348969</v>
       </c>
       <c r="I16" t="n">
-        <v>2.094337152250116</v>
+        <v>1.071242292653943</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731397401663372</v>
+        <v>4.684175104977732</v>
       </c>
       <c r="K16" t="n">
-        <v>19.19915627902105</v>
+        <v>22.56181888065314</v>
       </c>
       <c r="L16" t="n">
-        <v>43.30814379999292</v>
+        <v>42.34385947965423</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93024902583721</v>
+        <v>99.96430838159696</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.27170794895855</v>
+        <v>82.80977441322511</v>
       </c>
       <c r="C17" t="n">
-        <v>38.50356311544569</v>
+        <v>38.65924544361058</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4179551279072</v>
+        <v>1.381222561942196</v>
       </c>
       <c r="E17" t="n">
-        <v>12.54909477654149</v>
+        <v>11.98083589781884</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576675201198815</v>
+        <v>0.749806740772902</v>
       </c>
       <c r="G17" t="n">
-        <v>23.81159741130189</v>
+        <v>24.56485238738476</v>
       </c>
       <c r="H17" t="n">
-        <v>36.90052387193588</v>
+        <v>38.32398205028851</v>
       </c>
       <c r="I17" t="n">
-        <v>2.099447240402955</v>
+        <v>1.122782645187278</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735422000749259</v>
+        <v>4.686292129830637</v>
       </c>
       <c r="K17" t="n">
-        <v>17.72829205104144</v>
+        <v>17.19022558677489</v>
       </c>
       <c r="L17" t="n">
-        <v>43.69822273564</v>
+        <v>44.11311978861615</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93007790212712</v>
+        <v>99.9625908190016</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.97785443798591</v>
+        <v>84.47801901714355</v>
       </c>
       <c r="C18" t="n">
-        <v>36.53405121939821</v>
+        <v>39.38048895356545</v>
       </c>
       <c r="D18" t="n">
-        <v>1.332831237341751</v>
+        <v>1.382324304746934</v>
       </c>
       <c r="E18" t="n">
-        <v>12.08753949523475</v>
+        <v>12.5722552298054</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758220396680599</v>
+        <v>0.7504048298892781</v>
       </c>
       <c r="G18" t="n">
-        <v>22.38211930417745</v>
+        <v>24.70691673916189</v>
       </c>
       <c r="H18" t="n">
-        <v>36.92745050424521</v>
+        <v>38.35455146946558</v>
       </c>
       <c r="I18" t="n">
-        <v>1.750816021052402</v>
+        <v>2.021536257266491</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738877479253744</v>
+        <v>4.690030186807988</v>
       </c>
       <c r="K18" t="n">
-        <v>20.02214556201411</v>
+        <v>15.52198098285645</v>
       </c>
       <c r="L18" t="n">
-        <v>43.3854852396876</v>
+        <v>45.03019922862782</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94168202109991</v>
+        <v>99.93266916504972</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.0202184573554</v>
+        <v>81.54036481415694</v>
       </c>
       <c r="C19" t="n">
-        <v>35.84624334461687</v>
+        <v>36.75501582523725</v>
       </c>
       <c r="D19" t="n">
-        <v>1.297979857899283</v>
+        <v>1.278170035691692</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01478854786225</v>
+        <v>11.90593338431998</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586873383390705</v>
+        <v>0.7509219616242649</v>
       </c>
       <c r="G19" t="n">
-        <v>21.79686311363961</v>
+        <v>22.84531968502687</v>
       </c>
       <c r="H19" t="n">
-        <v>36.95019186685833</v>
+        <v>38.38098301009008</v>
       </c>
       <c r="I19" t="n">
-        <v>1.459911868137646</v>
+        <v>1.685774477252399</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741795864619191</v>
+        <v>4.693262260151655</v>
       </c>
       <c r="K19" t="n">
-        <v>20.97978154264462</v>
+        <v>18.45963518584305</v>
       </c>
       <c r="L19" t="n">
-        <v>43.12534133437596</v>
+        <v>44.72919520399564</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95136622163744</v>
+        <v>99.94384621507595</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.47680467996321</v>
+        <v>78.62206085842102</v>
       </c>
       <c r="C20" t="n">
-        <v>33.52767061758934</v>
+        <v>34.09617645498975</v>
       </c>
       <c r="D20" t="n">
-        <v>1.204590286796886</v>
+        <v>1.175341106300569</v>
       </c>
       <c r="E20" t="n">
-        <v>11.35319836345353</v>
+        <v>11.18237452363621</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590898584590183</v>
+        <v>0.7513694750795095</v>
       </c>
       <c r="G20" t="n">
-        <v>20.22858015056267</v>
+        <v>21.00741103499505</v>
       </c>
       <c r="H20" t="n">
-        <v>36.96979572066048</v>
+        <v>38.40385623420698</v>
       </c>
       <c r="I20" t="n">
-        <v>1.217238684661748</v>
+        <v>1.40564926495579</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744311615368865</v>
+        <v>4.696059219246933</v>
       </c>
       <c r="K20" t="n">
-        <v>23.52319532003683</v>
+        <v>21.37793914157895</v>
       </c>
       <c r="L20" t="n">
-        <v>42.90858095492556</v>
+        <v>44.47905733461874</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95944689255171</v>
+        <v>99.95317293118744</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.95619387176772</v>
+        <v>75.7264941795155</v>
       </c>
       <c r="C21" t="n">
-        <v>36.86135831922786</v>
+        <v>31.41615852568299</v>
       </c>
       <c r="D21" t="n">
-        <v>1.205479411283216</v>
+        <v>1.073893755700097</v>
       </c>
       <c r="E21" t="n">
-        <v>13.17198435450811</v>
+        <v>10.412518739199</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596501530154983</v>
+        <v>0.7517570932723204</v>
       </c>
       <c r="G21" t="n">
-        <v>21.7514522707154</v>
+        <v>19.19419597678676</v>
       </c>
       <c r="H21" t="n">
-        <v>38.50502475988973</v>
+        <v>38.42366810286041</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8147894660089</v>
+        <v>1.171978678744922</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747813456346865</v>
+        <v>4.698481832952003</v>
       </c>
       <c r="K21" t="n">
-        <v>18.04380612823228</v>
+        <v>24.27350582048449</v>
       </c>
       <c r="L21" t="n">
-        <v>45.03438718810014</v>
+        <v>44.27128984091707</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93955163556028</v>
+        <v>99.96095418708455</v>
       </c>
     </row>
   </sheetData>
